--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,9 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,9 +256,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -2116,13 +2116,13 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="94.82421875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="94.82421875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2358,19 +2358,19 @@
         <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AM2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>83</v>
@@ -2980,10 +2980,10 @@
         <v>83</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO7" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP7" t="s" s="2">
         <v>83</v>
@@ -3103,10 +3103,10 @@
         <v>83</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO8" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP8" t="s" s="2">
         <v>83</v>
@@ -3466,10 +3466,10 @@
         <v>83</v>
       </c>
       <c r="AN11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>83</v>
@@ -3710,10 +3710,10 @@
         <v>83</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>83</v>
@@ -3820,7 +3820,7 @@
         <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>83</v>
@@ -3829,16 +3829,16 @@
         <v>83</v>
       </c>
       <c r="AN14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="AO14" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -3954,10 +3954,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -4068,22 +4068,22 @@
         <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="AL16" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>83</v>
@@ -4191,19 +4191,19 @@
         <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>83</v>
@@ -4314,19 +4314,19 @@
         <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -4437,22 +4437,22 @@
         <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AO19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>83</v>
@@ -4569,13 +4569,13 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>83</v>
@@ -4696,13 +4696,13 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>83</v>
@@ -4817,10 +4817,10 @@
         <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>83</v>
@@ -4940,10 +4940,10 @@
         <v>83</v>
       </c>
       <c r="AN23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>83</v>
@@ -5062,13 +5062,13 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>83</v>
@@ -5186,10 +5186,10 @@
         <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>83</v>
@@ -5309,10 +5309,10 @@
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>83</v>
@@ -5431,13 +5431,13 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
@@ -5554,13 +5554,13 @@
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5677,13 +5677,13 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>83</v>
@@ -5800,13 +5800,13 @@
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
@@ -5925,13 +5925,13 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>83</v>
@@ -6050,13 +6050,13 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -6169,25 +6169,25 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AP33" t="s" s="2">
+      <c r="AQ33" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="34" hidden="true">
@@ -6294,22 +6294,22 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>83</v>
@@ -6423,16 +6423,16 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AO35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>83</v>
@@ -6542,22 +6542,22 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>83</v>
@@ -6667,22 +6667,22 @@
         <v>359</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AL37" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -6796,16 +6796,16 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AO38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>83</v>
@@ -6913,22 +6913,22 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>83</v>
@@ -7041,22 +7041,22 @@
         <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AO40" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -7169,13 +7169,13 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7291,22 +7291,22 @@
         <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AO42" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="43" hidden="true">
@@ -7419,13 +7419,13 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7539,22 +7539,22 @@
         <v>83</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AO44" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="45" hidden="true">
@@ -7667,13 +7667,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7787,22 +7787,22 @@
         <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AO46" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -7910,22 +7910,22 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AO47" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -8038,13 +8038,13 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
@@ -8162,10 +8162,10 @@
         <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
@@ -8285,10 +8285,10 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8410,10 +8410,10 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8528,13 +8528,13 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8649,13 +8649,13 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8771,16 +8771,16 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8896,16 +8896,16 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9025,10 +9025,10 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9143,13 +9143,13 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9266,13 +9266,13 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -9389,13 +9389,13 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
@@ -9514,13 +9514,13 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>83</v>
@@ -9638,10 +9638,10 @@
         <v>83</v>
       </c>
       <c r="AN61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
@@ -9761,10 +9761,10 @@
         <v>83</v>
       </c>
       <c r="AN62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>
@@ -9886,10 +9886,10 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>83</v>
@@ -10005,19 +10005,19 @@
         <v>83</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AO64" t="s" s="2">
+      <c r="AP64" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -10130,22 +10130,22 @@
         <v>83</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AO65" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AQ65" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="66" hidden="true">
@@ -10258,13 +10258,13 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10380,22 +10380,22 @@
         <v>83</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AO67" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="68" hidden="true">
@@ -10508,13 +10508,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-VitalSignsCPM.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
